--- a/simulation/bubble_dates.xlsx
+++ b/simulation/bubble_dates.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/emilrand/Desktop/ku/Bachelor/6. semester/ba/ba_repo/simulation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68CBF742-F380-F047-9E03-F03206369DED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2890764C-A9D6-DB4A-AF47-FA8EED910CE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3800" yWindow="2260" windowWidth="28240" windowHeight="17240" xr2:uid="{BF8102D9-532C-0B4A-83CA-46A6C7ECE445}"/>
   </bookViews>
   <sheets>
     <sheet name="Ark1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="23">
   <si>
     <t>Januar</t>
   </si>
@@ -102,6 +102,9 @@
   </si>
   <si>
     <t>ai slut</t>
+  </si>
+  <si>
+    <t>Kort sample start</t>
   </si>
 </sst>
 </file>
@@ -3945,7 +3948,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="289" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A289">
         <v>288</v>
       </c>
@@ -3957,7 +3960,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="290" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A290">
         <v>289</v>
       </c>
@@ -3969,7 +3972,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="291" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A291">
         <v>290</v>
       </c>
@@ -3981,7 +3984,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="292" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A292">
         <v>291</v>
       </c>
@@ -3993,7 +3996,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="293" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A293">
         <v>292</v>
       </c>
@@ -4005,7 +4008,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="294" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A294">
         <v>293</v>
       </c>
@@ -4017,7 +4020,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="295" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A295">
         <v>294</v>
       </c>
@@ -4029,7 +4032,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="296" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A296">
         <v>295</v>
       </c>
@@ -4041,7 +4044,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="297" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A297">
         <v>296</v>
       </c>
@@ -4053,7 +4056,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="298" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A298">
         <v>297</v>
       </c>
@@ -4065,7 +4068,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="299" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A299">
         <v>298</v>
       </c>
@@ -4077,7 +4080,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="300" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A300">
         <v>299</v>
       </c>
@@ -4089,7 +4092,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="301" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A301">
         <v>300</v>
       </c>
@@ -4101,19 +4104,22 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="302" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A302">
+    <row r="302" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A302" s="1">
         <v>301</v>
       </c>
-      <c r="B302" t="s">
+      <c r="B302" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C302">
+      <c r="C302" s="1">
         <f t="shared" si="4"/>
         <v>2015</v>
       </c>
-    </row>
-    <row r="303" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D302" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="303" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A303">
         <v>302</v>
       </c>
@@ -4125,7 +4131,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="304" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A304">
         <v>303</v>
       </c>

--- a/simulation/bubble_dates.xlsx
+++ b/simulation/bubble_dates.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/emilrand/Desktop/ku/Bachelor/6. semester/ba/ba_repo/simulation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2890764C-A9D6-DB4A-AF47-FA8EED910CE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8F02569-30E0-DE44-AB63-0BFB668598D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3800" yWindow="2260" windowWidth="28240" windowHeight="17240" xr2:uid="{BF8102D9-532C-0B4A-83CA-46A6C7ECE445}"/>
+    <workbookView xWindow="140" yWindow="780" windowWidth="17700" windowHeight="20340" xr2:uid="{BF8102D9-532C-0B4A-83CA-46A6C7ECE445}"/>
   </bookViews>
   <sheets>
     <sheet name="Ark1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="26">
   <si>
     <t>Januar</t>
   </si>
@@ -105,6 +105,15 @@
   </si>
   <si>
     <t>Kort sample start</t>
+  </si>
+  <si>
+    <t>Bubbles, vores BSADF resultater</t>
+  </si>
+  <si>
+    <t>dot com slut</t>
+  </si>
+  <si>
+    <t>covid slut</t>
   </si>
 </sst>
 </file>
@@ -487,16 +496,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8594D7BF-C905-BC4F-9198-7862CA647C22}">
-  <dimension ref="A1:D433"/>
+  <dimension ref="A1:E433"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.1640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.1640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="5.1640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>12</v>
       </c>
@@ -509,8 +519,11 @@
       <c r="D1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -521,7 +534,7 @@
         <v>1990</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -532,7 +545,7 @@
         <v>1990</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -543,7 +556,7 @@
         <v>1990</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -554,7 +567,7 @@
         <v>1990</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -565,7 +578,7 @@
         <v>1990</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -576,7 +589,7 @@
         <v>1990</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
@@ -587,7 +600,7 @@
         <v>1990</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
@@ -598,7 +611,7 @@
         <v>1990</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
@@ -609,7 +622,7 @@
         <v>1990</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
@@ -620,7 +633,7 @@
         <v>1990</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>11</v>
       </c>
@@ -631,7 +644,7 @@
         <v>1990</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>12</v>
       </c>
@@ -642,7 +655,7 @@
         <v>1990</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>13</v>
       </c>
@@ -654,7 +667,7 @@
         <v>1991</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>14</v>
       </c>
@@ -666,7 +679,7 @@
         <v>1991</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1257,7 +1270,7 @@
         <v>1995</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A65">
         <v>64</v>
       </c>
@@ -1269,7 +1282,7 @@
         <v>1995</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>65</v>
       </c>
@@ -1281,7 +1294,7 @@
         <v>1995</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A67">
         <v>66</v>
       </c>
@@ -1292,8 +1305,11 @@
         <f t="shared" si="0"/>
         <v>1995</v>
       </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="E67" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>67</v>
       </c>
@@ -1305,7 +1321,7 @@
         <v>1995</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A69">
         <v>68</v>
       </c>
@@ -1317,7 +1333,7 @@
         <v>1995</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A70">
         <v>69</v>
       </c>
@@ -1329,7 +1345,7 @@
         <v>1995</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A71">
         <v>70</v>
       </c>
@@ -1341,7 +1357,7 @@
         <v>1995</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A72">
         <v>71</v>
       </c>
@@ -1353,7 +1369,7 @@
         <v>1995</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A73">
         <v>72</v>
       </c>
@@ -1365,7 +1381,7 @@
         <v>1995</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A74">
         <v>73</v>
       </c>
@@ -1377,7 +1393,7 @@
         <v>1996</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A75">
         <v>74</v>
       </c>
@@ -1389,7 +1405,7 @@
         <v>1996</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A76">
         <v>75</v>
       </c>
@@ -1401,7 +1417,7 @@
         <v>1996</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A77">
         <v>76</v>
       </c>
@@ -1413,7 +1429,7 @@
         <v>1996</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A78">
         <v>77</v>
       </c>
@@ -1425,7 +1441,7 @@
         <v>1996</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A79">
         <v>78</v>
       </c>
@@ -1437,7 +1453,7 @@
         <v>1996</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A80">
         <v>79</v>
       </c>
@@ -2025,7 +2041,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A129">
         <v>128</v>
       </c>
@@ -2036,8 +2052,11 @@
         <f t="shared" si="1"/>
         <v>2000</v>
       </c>
-    </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="E129" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A130">
         <v>129</v>
       </c>
@@ -2049,7 +2068,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A131">
         <v>130</v>
       </c>
@@ -2061,7 +2080,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A132">
         <v>131</v>
       </c>
@@ -2073,7 +2092,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A133">
         <v>132</v>
       </c>
@@ -2085,7 +2104,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A134">
         <v>133</v>
       </c>
@@ -2097,7 +2116,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A135">
         <v>134</v>
       </c>
@@ -2109,7 +2128,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A136">
         <v>135</v>
       </c>
@@ -2121,7 +2140,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A137">
         <v>136</v>
       </c>
@@ -2133,7 +2152,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A138">
         <v>137</v>
       </c>
@@ -2145,7 +2164,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A139">
         <v>138</v>
       </c>
@@ -2157,7 +2176,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A140">
         <v>139</v>
       </c>
@@ -2169,7 +2188,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A141">
         <v>140</v>
       </c>
@@ -2181,7 +2200,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A142">
         <v>141</v>
       </c>
@@ -2193,7 +2212,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A143">
         <v>142</v>
       </c>
@@ -2205,7 +2224,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A144">
         <v>143</v>
       </c>
@@ -4719,7 +4738,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="353" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A353">
         <v>352</v>
       </c>
@@ -4731,7 +4750,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="354" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A354">
         <v>353</v>
       </c>
@@ -4743,7 +4762,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="355" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A355">
         <v>354</v>
       </c>
@@ -4755,7 +4774,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="356" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A356">
         <v>355</v>
       </c>
@@ -4767,7 +4786,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="357" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A357">
         <v>356</v>
       </c>
@@ -4779,7 +4798,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="358" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A358">
         <v>357</v>
       </c>
@@ -4791,7 +4810,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="359" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A359">
         <v>358</v>
       </c>
@@ -4803,7 +4822,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="360" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A360">
         <v>359</v>
       </c>
@@ -4815,7 +4834,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="361" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A361">
         <v>360</v>
       </c>
@@ -4827,7 +4846,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="362" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A362">
         <v>361</v>
       </c>
@@ -4839,7 +4858,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="363" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A363">
         <v>362</v>
       </c>
@@ -4851,7 +4870,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="364" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A364">
         <v>363</v>
       </c>
@@ -4863,7 +4882,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="365" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A365" s="1">
         <v>364</v>
       </c>
@@ -4877,8 +4896,11 @@
       <c r="D365" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="366" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E365" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="366" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A366">
         <v>365</v>
       </c>
@@ -4890,7 +4912,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="367" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A367">
         <v>366</v>
       </c>
@@ -4902,7 +4924,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="368" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A368">
         <v>367</v>
       </c>
@@ -5109,7 +5131,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="385" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A385">
         <v>384</v>
       </c>
@@ -5121,7 +5143,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="386" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A386">
         <v>385</v>
       </c>
@@ -5133,7 +5155,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="387" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A387">
         <v>386</v>
       </c>
@@ -5145,7 +5167,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="388" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A388">
         <v>387</v>
       </c>
@@ -5157,7 +5179,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="389" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A389">
         <v>388</v>
       </c>
@@ -5169,7 +5191,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="390" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A390">
         <v>389</v>
       </c>
@@ -5180,8 +5202,11 @@
         <f t="shared" si="5"/>
         <v>2022</v>
       </c>
-    </row>
-    <row r="391" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E390" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="391" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A391">
         <v>390</v>
       </c>
@@ -5193,7 +5218,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="392" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A392">
         <v>391</v>
       </c>
@@ -5205,7 +5230,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="393" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A393">
         <v>392</v>
       </c>
@@ -5217,7 +5242,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="394" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A394">
         <v>393</v>
       </c>
@@ -5229,7 +5254,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="395" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A395">
         <v>394</v>
       </c>
@@ -5241,7 +5266,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="396" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A396">
         <v>395</v>
       </c>
@@ -5253,7 +5278,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="397" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A397">
         <v>396</v>
       </c>
@@ -5265,7 +5290,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="398" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A398" s="1">
         <v>397</v>
       </c>
@@ -5280,7 +5305,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="399" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A399">
         <v>398</v>
       </c>
@@ -5292,7 +5317,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="400" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A400">
         <v>399</v>
       </c>
@@ -5304,7 +5329,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="401" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A401">
         <v>400</v>
       </c>
@@ -5316,7 +5341,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="402" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="402" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A402">
         <v>401</v>
       </c>
@@ -5327,8 +5352,11 @@
         <f t="shared" si="6"/>
         <v>2023</v>
       </c>
-    </row>
-    <row r="403" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="E402" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="403" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A403">
         <v>402</v>
       </c>
@@ -5340,7 +5368,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="404" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="404" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A404">
         <v>403</v>
       </c>
@@ -5352,7 +5380,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="405" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="405" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A405">
         <v>404</v>
       </c>
@@ -5364,7 +5392,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="406" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A406">
         <v>405</v>
       </c>
@@ -5376,7 +5404,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="407" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="407" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A407">
         <v>406</v>
       </c>
@@ -5388,7 +5416,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="408" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A408">
         <v>407</v>
       </c>
@@ -5400,7 +5428,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="409" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A409">
         <v>408</v>
       </c>
@@ -5412,7 +5440,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="410" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A410">
         <v>409</v>
       </c>
@@ -5424,7 +5452,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="411" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="411" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A411">
         <v>410</v>
       </c>
@@ -5436,7 +5464,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="412" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="412" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A412">
         <v>411</v>
       </c>
@@ -5448,7 +5476,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="413" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A413">
         <v>412</v>
       </c>
@@ -5460,7 +5488,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="414" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="414" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A414">
         <v>413</v>
       </c>
@@ -5472,7 +5500,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="415" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="415" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A415">
         <v>414</v>
       </c>
@@ -5484,7 +5512,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="416" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A416">
         <v>415</v>
       </c>
@@ -5688,7 +5716,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="433" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="433" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A433" s="1">
         <v>432</v>
       </c>
@@ -5700,6 +5728,9 @@
         <v>2025</v>
       </c>
       <c r="D433" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E433" t="s">
         <v>21</v>
       </c>
     </row>
